--- a/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten</t>
+          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,71</t>
+          <t>4,78; 7,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,56</t>
+          <t>6,84; 11,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,32</t>
+          <t>4,38; 10,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,39</t>
+          <t>6,51; 10,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,66</t>
+          <t>7,36; 8,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,83</t>
+          <t>6,17; 8,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,45</t>
+          <t>7,32; 10,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,04</t>
+          <t>5,39; 10,03</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,73</t>
+          <t>6,46; 7,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 8,77</t>
+          <t>7,51; 8,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,27</t>
+          <t>6,85; 8,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,07</t>
+          <t>6,11; 7,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,7</t>
+          <t>7,42; 8,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,77</t>
+          <t>6,65; 7,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 7,17</t>
+          <t>6,39; 7,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 8,52</t>
+          <t>7,63; 8,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,79</t>
+          <t>6,85; 7,82</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,74</t>
+          <t>6,55; 8,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,92</t>
+          <t>6,81; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,63</t>
+          <t>5,86; 7,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,73</t>
+          <t>6,23; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,97</t>
+          <t>6,29; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,33</t>
+          <t>5,81; 7,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,89</t>
+          <t>6,6; 7,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 8,08</t>
+          <t>6,79; 8,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,17</t>
+          <t>6,05; 7,31</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,71</t>
+          <t>6,57; 7,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,6</t>
+          <t>7,56; 8,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,84</t>
+          <t>6,62; 7,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,21</t>
+          <t>6,43; 7,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,25</t>
+          <t>7,32; 8,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,4</t>
+          <t>6,5; 7,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,29</t>
+          <t>6,64; 7,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,27</t>
+          <t>7,54; 8,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,44</t>
+          <t>6,7; 7,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,8</t>
+          <t>4,72; 7,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,83</t>
+          <t>6,83; 11,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,65</t>
+          <t>6,52; 10,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,68</t>
+          <t>7,32; 8,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,87</t>
+          <t>6,18; 8,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,3</t>
+          <t>7,39; 10,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,03</t>
+          <t>5,38; 9,89</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,72</t>
+          <t>6,51; 7,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,73</t>
+          <t>7,49; 8,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,36</t>
+          <t>6,84; 8,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,09</t>
+          <t>6,06; 7,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,69</t>
+          <t>7,46; 8,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,77</t>
+          <t>6,67; 7,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,13</t>
+          <t>6,41; 7,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 8,52</t>
+          <t>7,65; 8,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,82</t>
+          <t>6,87; 7,8</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,73</t>
+          <t>6,43; 8,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,8</t>
+          <t>6,81; 8,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,78</t>
+          <t>5,82; 7,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,77</t>
+          <t>6,25; 7,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,97</t>
+          <t>6,28; 7,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,44</t>
+          <t>5,83; 7,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,86</t>
+          <t>6,53; 7,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,15</t>
+          <t>6,75; 8,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,31</t>
+          <t>6,1; 7,26</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,65</t>
+          <t>6,62; 7,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,66</t>
+          <t>7,53; 8,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,82</t>
+          <t>6,62; 7,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 7,25</t>
+          <t>6,46; 7,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,25</t>
+          <t>7,29; 8,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,42</t>
+          <t>6,53; 7,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,28</t>
+          <t>6,66; 7,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,25</t>
+          <t>7,53; 8,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,44</t>
+          <t>6,7; 7,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,76</t>
+          <t>6,57; 10,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,71</t>
+          <t>7,33; 8,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,17</t>
+          <t>6,0; 12,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,26</t>
+          <t>4,77; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,59</t>
+          <t>6,8; 11,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,0</t>
+          <t>4,46; 10,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,57</t>
+          <t>6,32; 8,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,22</t>
+          <t>7,32; 10,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,89</t>
+          <t>5,35; 10,04</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>8,06</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,45</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,58</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6,13; 7,07</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7,42; 8,7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6,62; 7,77</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>6,51; 7,73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>7,49; 8,77</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,84; 8,34</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,06; 7,08</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,46; 8,66</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,75</t>
+          <t>6,79; 8,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,13</t>
+          <t>6,4; 7,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 8,51</t>
+          <t>7,62; 8,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,8</t>
+          <t>6,91; 7,79</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,06</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,48</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,45</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,72</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,68</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,64</t>
+          <t>6,23; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,9</t>
+          <t>6,31; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,67</t>
+          <t>5,79; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,77</t>
+          <t>6,45; 8,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 7,95</t>
+          <t>6,81; 8,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,4</t>
+          <t>5,77; 7,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,9</t>
+          <t>6,58; 7,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,02</t>
+          <t>6,78; 8,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,26</t>
+          <t>6,0; 7,17</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,75</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,05</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,03</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,62</t>
+          <t>6,41; 7,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,6</t>
+          <t>7,24; 8,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,78</t>
+          <t>6,5; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,28</t>
+          <t>6,6; 7,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,23</t>
+          <t>7,54; 8,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,45</t>
+          <t>6,65; 7,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,3</t>
+          <t>6,63; 7,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,25</t>
+          <t>7,54; 8,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,46</t>
+          <t>6,71; 7,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,89</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.61177297570291</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.895084535967501</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8.200481652118102</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.503622505303076</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>8.635756721040645</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.892811447280724</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>7.143533395202092</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>8.324119328874385</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.360320219849524</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,57; 10,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 8,66</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 12,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 7,71</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 11,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,46; 10,32</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 8,83</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,32; 10,45</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,35; 10,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.573796504645537</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.331407772143055</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.768369700575129</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>6.802027462539623</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.455625788858357</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>6.322479893349721</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.321071763622071</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.345839843936169</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.38695736720885</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.661906814066906</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.714323113240818</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.56030859397603</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.31665327760688</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>8.832977371050578</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10.44856068166695</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>10.04201034771443</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,58</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,74</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>6,13; 7,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 8,7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,62; 7,77</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,51; 7,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 8,77</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,79; 8,27</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,4; 7,17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,62; 8,52</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6,91; 7,79</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.58087152894857</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.052471313083171</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.167551266779524</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.92446428945694</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>8.059685881453788</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7.450531704307698</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>6.735367321762283</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>8.056030027607097</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.303722654679548</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,48</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,72</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,68</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7,38</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6.132967640309014</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.422414360546459</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6.624898329926105</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>6.506953532258708</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.492107428790097</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>6.791034493165849</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.402428843758257</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.619370986047397</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6.906419593522513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,23; 7,73</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,31; 7,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,79; 7,33</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6,45; 8,74</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 8,92</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,77; 7,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,58; 7,89</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,78; 8,08</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6,0; 7,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.067253939096189</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.697876621962916</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.768632040329103</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.733217497781883</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.76838309716012</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>8.270213433391966</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>7.170182490701956</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8.524477792572174</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7.789078168854123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,107 +845,215 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.992295518272554</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.059134713499224</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.475536073693738</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>7.447699683737599</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.716484649356312</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.681350609608429</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.205153057929275</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>7.381514483749882</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6.569889064570036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,41; 7,21</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,24; 8,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 7,4</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6,6; 7,71</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 8,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,65; 7,84</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,63; 7,29</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 8,27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6,71; 7,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.225008364141646</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.309022690530726</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.790136383627712</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>6.452478444675608</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.809277187648433</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.768075027880688</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.584912631873009</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>6.77984456214204</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>6.001769917059276</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.731948428974696</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.970434431431918</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.332549874468977</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>8.741706664205994</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.923088065720261</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.634495082148804</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.887355056858834</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>8.084617904967365</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7.171816617250101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.811854878649752</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.75216690274168</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.959649362999465</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7.053143212888728</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>8.027161076087387</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.181663256953189</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>6.921032397631145</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>7.889823322883939</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.066219650662475</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.412559744593956</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7.242190413764787</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>6.495554457079209</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>6.595158176679551</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.535800690806722</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6.649275634563104</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>6.629518524789297</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7.535169563389721</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>6.710514255879593</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.211088905541121</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.247859579546075</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.396067577476522</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.711707834475336</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.598412508445227</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.842842043538039</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.292317434553079</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>8.265786637781819</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.442897687289489</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1061,13 +1062,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
